--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,6 +934,108 @@
           <t>Åtgärdsprogram för kalktallskogar</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122386326</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90797</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Låshålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483341</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6988771</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>122386326</v>
       </c>
       <c r="B4" t="n">
-        <v>90797</v>
+        <v>90807</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>122386326</v>
       </c>
       <c r="B4" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>122386326</v>
       </c>
       <c r="B4" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>122386326</v>
       </c>
       <c r="B4" t="n">
-        <v>90826</v>
+        <v>90831</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,11 +954,6 @@
       </c>
       <c r="E4" t="n">
         <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>122386326</v>
       </c>
       <c r="B4" t="n">
-        <v>90831</v>
+        <v>90844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,6 +954,11 @@
       </c>
       <c r="E4" t="n">
         <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>122386326</v>
       </c>
       <c r="B4" t="n">
-        <v>90844</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>122386326</v>
       </c>
       <c r="B4" t="n">
-        <v>90857</v>
+        <v>90851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>122386326</v>
       </c>
       <c r="B4" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>122386326</v>
       </c>
       <c r="B4" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>17084216</v>
       </c>
       <c r="B2" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483410.0416184874</v>
+        <v>483410</v>
       </c>
       <c r="R2" t="n">
-        <v>6988788.03430689</v>
+        <v>6988788</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,19 +752,9 @@
           <t>2014-09-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,12 +794,7 @@
         <v>17084217</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,7 +816,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483410.0416184874</v>
+        <v>483410</v>
       </c>
       <c r="R3" t="n">
-        <v>6988788.03430689</v>
+        <v>6988788</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,19 +868,9 @@
           <t>2014-09-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,108 +904,6 @@
           <t>Åtgärdsprogram för kalktallskogar</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>122386326</v>
-      </c>
-      <c r="B4" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Låshålet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>483341</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6988771</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3846-2024 artfynd.xlsx
+++ b/artfynd/A 3846-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Åtgärdsprogram för kalktallskogar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17084216</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,8 +914,17 @@
           <t>Åtgärdsprogram för kalktallskogar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17084217</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>